--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AZ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116354126</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116354127</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112516</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112460</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112706</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112500</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363384</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112707</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,6 +2035,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112505</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119645925</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2191,6 +2261,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025195</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2303,6 +2378,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025196</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2400,6 +2480,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119645924</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2507,6 +2592,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025043</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2614,6 +2704,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025047</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2730,6 +2825,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025061</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2837,6 +2937,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025070</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2944,6 +3049,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025079</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3055,6 +3165,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025001</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3166,6 +3281,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025002</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3277,6 +3397,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025009</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3388,6 +3513,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025010</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3499,6 +3629,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025011</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3610,6 +3745,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025026</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3721,6 +3861,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025029</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3837,6 +3982,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025045</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3953,6 +4103,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025055</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4069,6 +4224,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025059</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4185,6 +4345,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025063</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4301,6 +4466,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025066</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4403,6 +4573,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025003</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4505,6 +4680,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025006</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4607,6 +4787,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025013</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4709,6 +4894,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025016</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4811,6 +5001,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025033</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4913,6 +5108,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025050</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5024,6 +5224,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025076</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5135,6 +5340,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025077</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5246,6 +5456,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025080</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5357,6 +5572,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025021</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5468,6 +5688,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5570,6 +5795,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025015</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5672,6 +5902,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025024</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5774,6 +6009,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025048</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5881,6 +6121,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025058</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5988,6 +6233,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025069</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6095,6 +6345,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025073</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6197,6 +6452,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025074</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6304,6 +6564,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025083</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6406,6 +6671,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025082</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6517,6 +6787,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025004</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6628,6 +6903,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025008</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6739,6 +7019,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025012</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6850,6 +7135,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025028</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6961,6 +7251,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025035</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7063,6 +7358,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025038</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7179,6 +7479,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025062</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7276,6 +7581,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363301</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7387,6 +7697,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025000</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7503,6 +7818,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025037</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7610,6 +7930,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025085</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7726,6 +8051,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025071</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7843,6 +8173,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135024998</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7955,6 +8290,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025005</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8067,6 +8407,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025022</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8179,6 +8524,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025027</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8291,6 +8641,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025034</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8403,6 +8758,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025046</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8515,6 +8875,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025049</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8632,6 +8997,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025053</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8743,6 +9113,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025075</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8854,6 +9229,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025084</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8965,6 +9345,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135025087</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9062,6 +9447,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112555</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9159,6 +9549,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112596</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9267,6 +9662,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112674</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9375,6 +9775,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112675</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9483,6 +9888,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112676</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9591,6 +10001,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112677</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9699,6 +10114,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112678</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9807,6 +10227,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112679</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9915,6 +10340,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112680</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10023,6 +10453,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112681</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10131,6 +10566,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112682</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10239,6 +10679,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112683</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10347,6 +10792,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112684</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10455,6 +10905,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112686</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10563,6 +11018,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112687</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10671,6 +11131,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112688</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10779,6 +11244,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112689</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10887,6 +11357,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112691</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10984,6 +11459,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112639</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11086,8 +11566,111 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -2156,7 +2156,7 @@
         <v>135025195</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>135025196</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>135025043</v>
       </c>
       <c r="B18" t="n">
-        <v>111257</v>
+        <v>111315</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>135025047</v>
       </c>
       <c r="B19" t="n">
-        <v>111257</v>
+        <v>111315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135025061</v>
       </c>
       <c r="B20" t="n">
-        <v>111257</v>
+        <v>111315</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>135025070</v>
       </c>
       <c r="B21" t="n">
-        <v>111257</v>
+        <v>111315</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>135025079</v>
       </c>
       <c r="B22" t="n">
-        <v>111257</v>
+        <v>111315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>135025001</v>
       </c>
       <c r="B23" t="n">
-        <v>111471</v>
+        <v>111529</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>135025002</v>
       </c>
       <c r="B24" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135025009</v>
       </c>
       <c r="B25" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>135025010</v>
       </c>
       <c r="B26" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>135025011</v>
       </c>
       <c r="B27" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>135025026</v>
       </c>
       <c r="B28" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>135025029</v>
       </c>
       <c r="B29" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>135025045</v>
       </c>
       <c r="B30" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>135025055</v>
       </c>
       <c r="B31" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>135025059</v>
       </c>
       <c r="B32" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>135025063</v>
       </c>
       <c r="B33" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>135025066</v>
       </c>
       <c r="B34" t="n">
-        <v>99173</v>
+        <v>99220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>135025003</v>
       </c>
       <c r="B35" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>135025006</v>
       </c>
       <c r="B36" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>135025013</v>
       </c>
       <c r="B37" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>135025016</v>
       </c>
       <c r="B38" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>135025033</v>
       </c>
       <c r="B39" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>135025050</v>
       </c>
       <c r="B40" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135025076</v>
       </c>
       <c r="B41" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>135025077</v>
       </c>
       <c r="B42" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>135025080</v>
       </c>
       <c r="B43" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>135025021</v>
       </c>
       <c r="B44" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>135025025</v>
       </c>
       <c r="B45" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>135025015</v>
       </c>
       <c r="B46" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>135025024</v>
       </c>
       <c r="B47" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>135025048</v>
       </c>
       <c r="B48" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>135025058</v>
       </c>
       <c r="B49" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135025069</v>
       </c>
       <c r="B50" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135025073</v>
       </c>
       <c r="B51" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135025074</v>
       </c>
       <c r="B52" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>135025083</v>
       </c>
       <c r="B53" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>135025082</v>
       </c>
       <c r="B54" t="n">
-        <v>106894</v>
+        <v>106949</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>135025004</v>
       </c>
       <c r="B55" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>135025008</v>
       </c>
       <c r="B56" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>135025012</v>
       </c>
       <c r="B57" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>135025028</v>
       </c>
       <c r="B58" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>135025035</v>
       </c>
       <c r="B59" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>135025038</v>
       </c>
       <c r="B60" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>135025062</v>
       </c>
       <c r="B61" t="n">
-        <v>102318</v>
+        <v>102367</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>135025000</v>
       </c>
       <c r="B63" t="n">
-        <v>103762</v>
+        <v>103813</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>135025037</v>
       </c>
       <c r="B64" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135025085</v>
       </c>
       <c r="B65" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135025071</v>
       </c>
       <c r="B66" t="n">
-        <v>103487</v>
+        <v>103538</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135024998</v>
       </c>
       <c r="B67" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>135025005</v>
       </c>
       <c r="B68" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>135025022</v>
       </c>
       <c r="B69" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>135025027</v>
       </c>
       <c r="B70" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>135025034</v>
       </c>
       <c r="B71" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135025046</v>
       </c>
       <c r="B72" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>135025049</v>
       </c>
       <c r="B73" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>135025053</v>
       </c>
       <c r="B74" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>135025075</v>
       </c>
       <c r="B75" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>135025084</v>
       </c>
       <c r="B76" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>135025087</v>
       </c>
       <c r="B77" t="n">
-        <v>99113</v>
+        <v>99160</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -2491,7 +2491,7 @@
         <v>135025043</v>
       </c>
       <c r="B18" t="n">
-        <v>111315</v>
+        <v>111342</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>135025047</v>
       </c>
       <c r="B19" t="n">
-        <v>111315</v>
+        <v>111342</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135025061</v>
       </c>
       <c r="B20" t="n">
-        <v>111315</v>
+        <v>111342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>135025070</v>
       </c>
       <c r="B21" t="n">
-        <v>111315</v>
+        <v>111342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>135025079</v>
       </c>
       <c r="B22" t="n">
-        <v>111315</v>
+        <v>111342</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>135025001</v>
       </c>
       <c r="B23" t="n">
-        <v>111529</v>
+        <v>111556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>135025002</v>
       </c>
       <c r="B24" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135025009</v>
       </c>
       <c r="B25" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>135025010</v>
       </c>
       <c r="B26" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>135025011</v>
       </c>
       <c r="B27" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>135025026</v>
       </c>
       <c r="B28" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>135025029</v>
       </c>
       <c r="B29" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>135025045</v>
       </c>
       <c r="B30" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>135025055</v>
       </c>
       <c r="B31" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>135025059</v>
       </c>
       <c r="B32" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>135025063</v>
       </c>
       <c r="B33" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>135025066</v>
       </c>
       <c r="B34" t="n">
-        <v>99220</v>
+        <v>99247</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>135025003</v>
       </c>
       <c r="B35" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>135025006</v>
       </c>
       <c r="B36" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>135025013</v>
       </c>
       <c r="B37" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>135025016</v>
       </c>
       <c r="B38" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>135025033</v>
       </c>
       <c r="B39" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>135025050</v>
       </c>
       <c r="B40" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135025076</v>
       </c>
       <c r="B41" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>135025077</v>
       </c>
       <c r="B42" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>135025080</v>
       </c>
       <c r="B43" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>135025021</v>
       </c>
       <c r="B44" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>135025025</v>
       </c>
       <c r="B45" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>135025015</v>
       </c>
       <c r="B46" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>135025024</v>
       </c>
       <c r="B47" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>135025048</v>
       </c>
       <c r="B48" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>135025058</v>
       </c>
       <c r="B49" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>135025069</v>
       </c>
       <c r="B50" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135025073</v>
       </c>
       <c r="B51" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135025074</v>
       </c>
       <c r="B52" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>135025083</v>
       </c>
       <c r="B53" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>135025082</v>
       </c>
       <c r="B54" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>135025004</v>
       </c>
       <c r="B55" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>135025008</v>
       </c>
       <c r="B56" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>135025012</v>
       </c>
       <c r="B57" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>135025028</v>
       </c>
       <c r="B58" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>135025035</v>
       </c>
       <c r="B59" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>135025038</v>
       </c>
       <c r="B60" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>135025062</v>
       </c>
       <c r="B61" t="n">
-        <v>102367</v>
+        <v>102394</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>135025000</v>
       </c>
       <c r="B63" t="n">
-        <v>103813</v>
+        <v>103840</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>135025037</v>
       </c>
       <c r="B64" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135025085</v>
       </c>
       <c r="B65" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135025071</v>
       </c>
       <c r="B66" t="n">
-        <v>103538</v>
+        <v>103565</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>135024998</v>
       </c>
       <c r="B67" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>135025005</v>
       </c>
       <c r="B68" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>135025022</v>
       </c>
       <c r="B69" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>135025027</v>
       </c>
       <c r="B70" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>135025034</v>
       </c>
       <c r="B71" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135025046</v>
       </c>
       <c r="B72" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>135025049</v>
       </c>
       <c r="B73" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>135025053</v>
       </c>
       <c r="B74" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>135025075</v>
       </c>
       <c r="B75" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>135025084</v>
       </c>
       <c r="B76" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>135025087</v>
       </c>
       <c r="B77" t="n">
-        <v>99160</v>
+        <v>99187</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96446</v>
+        <v>96617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96617</v>
+        <v>96618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96619</v>
+        <v>96625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27759-2026 artfynd.xlsx
+++ b/artfynd/A 27759-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>74112706</v>
       </c>
       <c r="B8" t="n">
-        <v>96625</v>
+        <v>96626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
